--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0150.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0150.xlsx
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Không, ta đã bảo rồi... Nghe này, nhóc à. Có nhiều việc quan trọng không kém gì làm Gladiator. Việc của ta là ghi lại những khoảnh khắc anh hùng của họ.</t>
+          <t>Không, tao đã bảo rồi... Nghe này, nhóc à. Có nhiều việc quan trọng không kém gì làm Gladiator. Việc của tao là ghi lại những khoảnh khắc anh hùng của họ.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Giờ thì ta đã nắm được nhịp điệu rồi!</t>
+          <t>Giờ thì tao đã nắm được nhịp điệu rồi!</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ừ. Mỗi lần vào quán rượu là ngươi lại say bí tỉ. Ta còn không biết phải mở lời thế nào nếu ngươi không ghé quán cà phê.</t>
+          <t>Ừ. Mỗi lần vào quán rượu là mày lại say bí tỉ. Tao còn không biết phải mở lời thế nào nếu mày không ghé quán cà phê.</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Eww! Thằng biến thái này vừa liếm mặt ta!</t>
+          <t>Eww! Thằng biến thái này vừa liếm mặt tao!</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Được rồi. Được rồi. Đừng lại gần nữa, và cũng đừng có mà liếm mặt ta nhé!</t>
+          <t>Được rồi. Được rồi. Đừng lại gần nữa, và cũng đừng có mà liếm mặt tao nhé!</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Thế là ta pha nước ép với nước lã rồi bán cho tụi nó như thuốc chữa bách bệnh!</t>
+          <t>Thế là tao pha nước ép với nước lã rồi bán cho tụi nó như thuốc chữa bách bệnh!</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Cơ bắp... Cơ bắp Septimont... Chúng làm ta phát điên lên được. Phải nghĩ gì khác mới được...</t>
+          <t>Cơ bắp... Cơ bắp Septimont... Chúng làm tao phát điên lên được. Phải nghĩ gì khác mới được...</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Vậy à? Tốt quá. Gần đây ta thấy mọi người bắt đầu nhắc về cô ấy nhiều hơn. Giống như những ngày xưa ấy nhỉ...</t>
+          <t>Vậy à? Tốt quá. Gần đây tao thấy mọi người bắt đầu nhắc về cô ấy nhiều hơn. Giống như những ngày xưa ấy nhỉ...</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Để ta đi trước. Nhanh gọn lẹ! Bình tĩnh và vững vàng! Mạnh mẽ và kiên định!</t>
+          <t>Để tao đi trước. Nhanh gọn lẹ! Bình tĩnh và vững vàng! Mạnh mẽ và kiên định!</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Sau bao chuyến đi, ta phát hiện ra khoảnh khắc hoàn hảo để làm điều đó là khi chúng ta lên đến đỉnh núi, biển cả dần hiện ra trước mắt. Lãng mạn, phải không?</t>
+          <t>Sau bao chuyến đi, tao phát hiện ra khoảnh khắc hoàn hảo để làm điều đó là khi chúng ta lên đến đỉnh núi, biển cả dần hiện ra trước mắt. Lãng mạn, phải không?</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Tuần này ta tham gia trận đấu tập nữa nhưng thua ở vòng chung kết. Ta sẽ đăng ký trận thật khi nào thắng liên tiếp ba vòng.</t>
+          <t>Tuần này tao tham gia trận đấu tập nữa nhưng thua ở vòng chung kết. Tao sẽ đăng ký trận thật khi nào thắng liên tiếp ba vòng.</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Cuộc săn à? Sao lại là ta? Cậu biết ta không biết đánh nhau mà...</t>
+          <t>Cuộc săn à? Sao lại là tao? Cậu biết tao không biết đánh nhau mà...</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Ta biết cậu sợ Đại Triều. Nhưng một khi đã tham gia săn lùng, nó sẽ giúp cậu giảm bớt căng thẳng đấy.</t>
+          <t>Tao biết cậu sợ Đại Triều. Nhưng một khi đã tham gia săn lùng, nó sẽ giúp cậu giảm bớt căng thẳng đấy.</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Chúc săn bắn vui vẻ! Đội mà cậu ủng hộ sắp phải đối đầu với đội của bạn ta đấy. Hôm nay là ngày kết thúc chuỗi thắng của cậu rồi!</t>
+          <t>Chúc săn bắn vui vẻ! Đội mà cậu ủng hộ sắp phải đối đầu với đội của bạn tao đấy. Hôm nay là ngày kết thúc chuỗi thắng của cậu rồi!</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Biển Sâu! Sentinel! Cậu có nghe lũ Septimontians bàn tán gì về mấy chuyện này không?</t>
+          <t>Giáo Đoàn Biển Sâu! Sentinel! Mày có nghe lũ Septimontians bàn tán gì về mấy chuyện này không?</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Để ta yên! Chỉ vì ngươi cao to đẹp trai mà nghĩ có thể tán tỉnh ta à? Ta đang không có hứng.</t>
+          <t>Để tao yên! Chỉ vì mày cao to đẹp trai mà nghĩ có thể tán tỉnh tao à? Tao đang không có hứng.</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Ta không thèm quan tâm ngươi có vũ khí đầy đủ hay không. Chỉ cần ngươi đẩy ta, ta sẽ cho ngươi bay một cú đấm rồi biến đi!</t>
+          <t>Tao không thèm quan tâm mày có vũ khí đầy đủ hay không. Chỉ cần mày đẩy tao, tao sẽ cho mày bay một cú đấm rồi biến đi!</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Symmonds, cậu ướt đẫm mồ hôi như vừa bò lên từ đại dương vậy! Nghỉ ngơi đi thôi.</t>
+          <t>Symmonds, mày ướt đẫm mồ hôi như vừa bò lên từ đại dương vậy! Nghỉ ngơi đi thôi.</t>
         </is>
       </c>
     </row>
